--- a/data/trans_dic/P12_3_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P12_3_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces</t>
+          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,35; 10,75</t>
+          <t>7,42; 11,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,84; 16,63</t>
+          <t>11,67; 16,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,06; 15,68</t>
+          <t>10,93; 15,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,1; 21,15</t>
+          <t>14,9; 21,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,73; 13,28</t>
+          <t>9,89; 13,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,7; 21,05</t>
+          <t>16,65; 21,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,84; 24,54</t>
+          <t>18,64; 24,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,76; 27,37</t>
+          <t>22,61; 27,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,25; 11,73</t>
+          <t>9,22; 11,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,15; 18,31</t>
+          <t>15,22; 18,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,07; 19,71</t>
+          <t>16,0; 19,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,12; 24,08</t>
+          <t>20,25; 23,88</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,46</t>
+          <t>2,68; 4,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 7,46</t>
+          <t>5,08; 7,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 6,91</t>
+          <t>4,85; 7,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,99</t>
+          <t>5,82; 9,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 7,71</t>
+          <t>5,37; 7,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,32; 12,4</t>
+          <t>9,28; 12,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,65; 10,27</t>
+          <t>7,63; 10,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 12,3</t>
+          <t>8,16; 12,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 5,66</t>
+          <t>4,12; 5,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,48; 9,41</t>
+          <t>7,45; 9,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,53; 8,14</t>
+          <t>6,5; 8,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 10,74</t>
+          <t>7,61; 10,76</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,43</t>
+          <t>1,44; 4,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,97</t>
+          <t>2,14; 5,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,75</t>
+          <t>3,59; 7,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,44; 13,71</t>
+          <t>6,55; 13,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,25</t>
+          <t>4,8; 9,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 9,42</t>
+          <t>4,15; 9,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,32</t>
+          <t>2,87; 6,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,15; 9,92</t>
+          <t>6,04; 9,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,15</t>
+          <t>3,36; 6,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,84</t>
+          <t>3,32; 6,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,3</t>
+          <t>3,72; 6,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 10,65</t>
+          <t>6,87; 10,98</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 5,86</t>
+          <t>4,34; 5,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 9,04</t>
+          <t>7,05; 9,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 8,33</t>
+          <t>6,56; 8,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,72; 11,27</t>
+          <t>7,73; 11,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 9,46</t>
+          <t>7,61; 9,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,1; 14,42</t>
+          <t>12,1; 14,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,68; 12,94</t>
+          <t>10,5; 12,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,62; 14,34</t>
+          <t>10,81; 14,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 7,46</t>
+          <t>6,19; 7,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,9; 11,45</t>
+          <t>9,98; 11,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,86; 10,28</t>
+          <t>8,79; 10,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,04; 12,57</t>
+          <t>10,07; 12,58</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces</t>
+          <t>Población que se sintió desanimada y triste siempre, casi siempre o muchas veces (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>75831; 110877</t>
+          <t>76520; 114700</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>115167; 161700</t>
+          <t>113506; 159594</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83344; 118134</t>
+          <t>82327; 119599</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77698; 108813</t>
+          <t>76637; 108353</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>127975; 174620</t>
+          <t>130094; 178520</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>223288; 281437</t>
+          <t>222612; 280825</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>186966; 243589</t>
+          <t>185052; 239296</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>171485; 206234</t>
+          <t>170348; 205725</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>217188; 275206</t>
+          <t>216440; 272971</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>349795; 422745</t>
+          <t>351443; 428386</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>280511; 344129</t>
+          <t>279416; 346105</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>255071; 305393</t>
+          <t>256811; 302862</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42582; 75448</t>
+          <t>45383; 75933</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>103290; 146244</t>
+          <t>99655; 145529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>99977; 143183</t>
+          <t>100455; 145165</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124844; 228498</t>
+          <t>133149; 226469</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>85771; 122488</t>
+          <t>85184; 123429</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>163449; 217465</t>
+          <t>162814; 218258</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>151718; 203848</t>
+          <t>151340; 204303</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>172541; 275174</t>
+          <t>182404; 282020</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>137088; 185833</t>
+          <t>135310; 185292</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>277845; 349761</t>
+          <t>276713; 349679</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>264766; 330395</t>
+          <t>263478; 335551</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>343445; 485843</t>
+          <t>344452; 486800</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8102; 24431</t>
+          <t>7933; 25905</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9660; 28656</t>
+          <t>10271; 28325</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19370; 42382</t>
+          <t>19632; 43192</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41664; 88635</t>
+          <t>42359; 87922</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22833; 44045</t>
+          <t>22879; 44389</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18045; 43085</t>
+          <t>18974; 41763</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14831; 34643</t>
+          <t>15724; 35700</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40642; 65538</t>
+          <t>39901; 63504</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34051; 63164</t>
+          <t>34527; 62686</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32450; 64183</t>
+          <t>31116; 62761</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38616; 69029</t>
+          <t>40784; 69283</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>90079; 139237</t>
+          <t>89791; 143518</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>143463; 192159</t>
+          <t>142339; 191186</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>242943; 308587</t>
+          <t>240835; 308516</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>219975; 280837</t>
+          <t>221081; 280741</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>266346; 388799</t>
+          <t>266464; 385689</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>254823; 319623</t>
+          <t>257068; 322135</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>429397; 511524</t>
+          <t>429174; 516871</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>376649; 456212</t>
+          <t>370195; 454657</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>387516; 523357</t>
+          <t>394465; 528600</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>413707; 496793</t>
+          <t>411795; 487619</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>689390; 796903</t>
+          <t>694813; 804004</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>610917; 708723</t>
+          <t>606480; 713486</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>712845; 892005</t>
+          <t>714598; 893301</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P12_3_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P12_3_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,42; 11,12</t>
+          <t>7,46; 11,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,67; 16,41</t>
+          <t>11,69; 16,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,93; 15,88</t>
+          <t>11,22; 15,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,9; 21,06</t>
+          <t>14,77; 20,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,89; 13,57</t>
+          <t>9,93; 13,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,65; 21,01</t>
+          <t>16,85; 21,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,64; 24,11</t>
+          <t>18,59; 24,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,61; 27,3</t>
+          <t>23,54; 28,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,22; 11,63</t>
+          <t>9,28; 11,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,22; 18,55</t>
+          <t>15,34; 18,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,0; 19,82</t>
+          <t>16,03; 19,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,25; 23,88</t>
+          <t>20,45; 24,31</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 4,48</t>
+          <t>2,56; 4,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 7,42</t>
+          <t>5,27; 7,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,01</t>
+          <t>4,74; 6,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 9,9</t>
+          <t>8,37; 11,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 7,77</t>
+          <t>5,35; 7,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,28; 12,45</t>
+          <t>9,38; 12,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,63; 10,3</t>
+          <t>7,62; 10,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,16; 12,61</t>
+          <t>11,28; 13,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 5,65</t>
+          <t>4,21; 5,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 9,41</t>
+          <t>7,48; 9,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,5; 8,27</t>
+          <t>6,44; 8,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 10,76</t>
+          <t>10,1; 12,1</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,7</t>
+          <t>1,38; 4,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,9</t>
+          <t>2,02; 5,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,9</t>
+          <t>3,64; 7,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 13,6</t>
+          <t>6,05; 10,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 9,32</t>
+          <t>4,73; 9,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 9,13</t>
+          <t>3,91; 9,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,51</t>
+          <t>2,87; 6,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,04; 9,62</t>
+          <t>6,88; 10,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,1</t>
+          <t>3,36; 6,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,69</t>
+          <t>3,49; 6,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,33</t>
+          <t>3,64; 6,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 10,98</t>
+          <t>6,88; 9,66</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 5,83</t>
+          <t>4,37; 5,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 9,04</t>
+          <t>7,07; 9,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,56; 8,32</t>
+          <t>6,55; 8,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,73; 11,18</t>
+          <t>9,45; 11,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,61; 9,53</t>
+          <t>7,6; 9,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,1; 14,57</t>
+          <t>12,12; 14,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,5; 12,9</t>
+          <t>10,64; 12,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,81; 14,48</t>
+          <t>13,62; 15,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 7,33</t>
+          <t>6,24; 7,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,98; 11,55</t>
+          <t>9,99; 11,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,79; 10,34</t>
+          <t>8,85; 10,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,07; 12,58</t>
+          <t>11,92; 13,38</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91653</t>
+          <t>101832</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>187887</t>
+          <t>212479</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>279541</t>
+          <t>314311</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>76520; 114700</t>
+          <t>76976; 114049</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>113506; 159594</t>
+          <t>113690; 157785</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>82327; 119599</t>
+          <t>84525; 118508</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>76637; 108353</t>
+          <t>85396; 120247</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>130094; 178520</t>
+          <t>130646; 178859</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>222612; 280825</t>
+          <t>225273; 281540</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>185052; 239296</t>
+          <t>184530; 238948</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>170348; 205725</t>
+          <t>193072; 231392</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>216440; 272971</t>
+          <t>217841; 276516</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>351443; 428386</t>
+          <t>354249; 422869</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>279416; 346105</t>
+          <t>279883; 347130</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>256811; 302862</t>
+          <t>285928; 339862</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>189258</t>
+          <t>212671</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>238309</t>
+          <t>270203</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>427568</t>
+          <t>482874</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45383; 75933</t>
+          <t>43278; 75401</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>99655; 145529</t>
+          <t>103384; 145518</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>100455; 145165</t>
+          <t>98126; 143449</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>133149; 226469</t>
+          <t>186476; 245440</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>85184; 123429</t>
+          <t>84873; 123337</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>162814; 218258</t>
+          <t>164461; 218596</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>151340; 204303</t>
+          <t>151206; 203928</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>182404; 282020</t>
+          <t>244730; 301621</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>135310; 185292</t>
+          <t>138216; 187799</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>276713; 349679</t>
+          <t>277802; 352821</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>263478; 335551</t>
+          <t>261332; 331273</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>344452; 486800</t>
+          <t>444256; 532155</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58323</t>
+          <t>56809</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51482</t>
+          <t>62449</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>109804</t>
+          <t>119258</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7933; 25905</t>
+          <t>7623; 23913</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10271; 28325</t>
+          <t>9683; 28353</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19632; 43192</t>
+          <t>19931; 43013</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42359; 87922</t>
+          <t>43065; 74546</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22879; 44389</t>
+          <t>22525; 43807</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18974; 41763</t>
+          <t>17870; 42101</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15724; 35700</t>
+          <t>15734; 34953</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39901; 63504</t>
+          <t>50541; 79510</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34527; 62686</t>
+          <t>34576; 63233</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31116; 62761</t>
+          <t>32736; 62148</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40784; 69283</t>
+          <t>39882; 69185</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>89791; 143518</t>
+          <t>99494; 139680</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>339234</t>
+          <t>371313</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>477678</t>
+          <t>545131</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>816913</t>
+          <t>916443</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>142339; 191186</t>
+          <t>143211; 193234</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>240835; 308516</t>
+          <t>241425; 309872</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>221081; 280741</t>
+          <t>221048; 280771</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>266464; 385689</t>
+          <t>332342; 409314</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>257068; 322135</t>
+          <t>256718; 323281</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>429174; 516871</t>
+          <t>430209; 518371</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>370195; 454657</t>
+          <t>374912; 453707</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>394465; 528600</t>
+          <t>507320; 580638</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>411795; 487619</t>
+          <t>415159; 501040</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>694813; 804004</t>
+          <t>695808; 807260</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>606480; 713486</t>
+          <t>610454; 711189</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>714598; 893301</t>
+          <t>862977; 968920</t>
         </is>
       </c>
     </row>
